--- a/Admin/Course Attendance.xlsx
+++ b/Admin/Course Attendance.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A79DAE5-37B7-6D41-B2ED-CEF06E20A041}"/>
+  <xr:revisionPtr revIDLastSave="782" documentId="13_ncr:1_{10AACCFA-37B1-6D44-A367-828EAD02C19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C9BCFE-CD92-064E-8C35-07B60593FFD5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="29940" windowHeight="16700" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" activeTab="4" xr2:uid="{24CAAD2F-8633-184E-A7D2-D706FBAD8E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Information" sheetId="3" r:id="rId1"/>
     <sheet name="Informatics S2" sheetId="2" r:id="rId2"/>
     <sheet name="Informatics S3" sheetId="4" r:id="rId3"/>
     <sheet name="Informatics S1" sheetId="5" r:id="rId4"/>
+    <sheet name="Informatics S4" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="203">
   <si>
     <t>Class 1</t>
   </si>
@@ -98,9 +99,6 @@
     <t>sunny.wang14@education.nsw.gov.au</t>
   </si>
   <si>
-    <t>学生姓名</t>
-  </si>
-  <si>
     <t>年级</t>
   </si>
   <si>
@@ -320,9 +318,6 @@
     <t>Reddam House School Sydney</t>
   </si>
   <si>
-    <t>xxx</t>
-  </si>
-  <si>
     <t>Informatics in C++ Stage 1</t>
   </si>
   <si>
@@ -573,6 +568,87 @@
   </si>
   <si>
     <t>lijuanlin89@gmail.com</t>
+  </si>
+  <si>
+    <t>Class 17</t>
+  </si>
+  <si>
+    <t>Noey Chu</t>
+  </si>
+  <si>
+    <t>chuxiao0705@gmail.com</t>
+  </si>
+  <si>
+    <t>discuss 2026 AIO P1 - P5, review past units work</t>
+  </si>
+  <si>
+    <t>Review past weeks work, Branching 2</t>
+  </si>
+  <si>
+    <t>Dylan Sun</t>
+  </si>
+  <si>
+    <t>Looping 1</t>
+  </si>
+  <si>
+    <t>Review homework</t>
+  </si>
+  <si>
+    <t>Informatics in C++ Stage 4</t>
+  </si>
+  <si>
+    <t>Jerry Zi</t>
+  </si>
+  <si>
+    <t>Knox Grammar School</t>
+  </si>
+  <si>
+    <t>Jimmy Chen</t>
+  </si>
+  <si>
+    <t>Looping 2</t>
+  </si>
+  <si>
+    <t>16:30 - 18:30</t>
+  </si>
+  <si>
+    <t>Review homework, binary trees</t>
+  </si>
+  <si>
+    <t>10:00 - 12:00</t>
+  </si>
+  <si>
+    <t>Term test</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Nick Chen</t>
+  </si>
+  <si>
+    <t>Kellyville Ridge Public School</t>
+  </si>
+  <si>
+    <t>nickchen5188@gmail.com</t>
+  </si>
+  <si>
+    <t>xinkuangchen@gmail.com</t>
+  </si>
+  <si>
+    <t>jerry.zi2020@gmail.com</t>
+  </si>
+  <si>
+    <t>Stella Song</t>
+  </si>
+  <si>
+    <t>Kincoppal-Rose Bay School</t>
+  </si>
+  <si>
+    <t>Review term test, arrays</t>
+  </si>
+  <si>
+    <t>Struct, Files</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FB8569-CA3E-974B-8804-A3AC313A4BC3}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1060,19 +1136,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1083,7 +1159,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
@@ -1100,7 +1176,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
@@ -1117,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
@@ -1134,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
@@ -1145,16 +1221,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>2026</v>
@@ -1162,16 +1238,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7">
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E7">
         <v>2026</v>
@@ -1179,16 +1255,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E8">
         <v>2026</v>
@@ -1196,16 +1272,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E9">
         <v>2026</v>
@@ -1213,16 +1289,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E10">
         <v>2026</v>
@@ -1230,16 +1306,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E11">
         <v>2026</v>
@@ -1247,16 +1323,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E12">
         <v>2026</v>
@@ -1264,16 +1340,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B13">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>2026</v>
@@ -1281,16 +1357,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E14">
         <v>2026</v>
@@ -1298,16 +1374,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E15">
         <v>2026</v>
@@ -1315,16 +1391,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E16">
         <v>2026</v>
@@ -1332,16 +1408,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E17">
         <v>2026</v>
@@ -1349,16 +1425,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B18">
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E18">
         <v>2026</v>
@@ -1366,16 +1442,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B19">
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E19">
         <v>2026</v>
@@ -1383,16 +1459,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E20">
         <v>2026</v>
@@ -1400,16 +1476,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E21">
         <v>2026</v>
@@ -1417,13 +1493,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>2026</v>
@@ -1431,16 +1507,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B23">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E23">
         <v>2026</v>
@@ -1448,16 +1524,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B24">
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E24">
         <v>2026</v>
@@ -1465,16 +1541,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B25">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E25">
         <v>2026</v>
@@ -1482,18 +1558,100 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B26">
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D26" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E26">
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B28">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>199</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31">
         <v>2026</v>
       </c>
     </row>
@@ -1521,6 +1679,10 @@
     <hyperlink ref="D19" r:id="rId20" xr:uid="{5952183A-29A7-409D-93BF-AA0EF92E7186}"/>
     <hyperlink ref="D25" r:id="rId21" xr:uid="{B7D10D5A-C18F-BB49-B8EE-D11F6CB65EE2}"/>
     <hyperlink ref="D26" r:id="rId22" xr:uid="{C0986F85-3C11-3B46-B2A7-F42D92FF1B74}"/>
+    <hyperlink ref="D27" r:id="rId23" xr:uid="{A49967F4-97E8-ED48-AFDD-2AE509548965}"/>
+    <hyperlink ref="D30" r:id="rId24" xr:uid="{0672DD45-FBA4-4509-94EB-981D80C33F41}"/>
+    <hyperlink ref="D29" r:id="rId25" xr:uid="{C60D0B1E-4EDA-429D-8BB0-1D0F11F2720E}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{2C147886-F842-49CF-A033-59949333AA3E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1583,10 +1745,10 @@
         <v>16</v>
       </c>
       <c r="I2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -1594,7 +1756,7 @@
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
       <c r="P2" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -1617,25 +1779,25 @@
         <v>4</v>
       </c>
       <c r="I3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="P3" s="8"/>
     </row>
@@ -1656,7 +1818,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -1665,7 +1827,7 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -1685,31 +1847,31 @@
         <v>4</v>
       </c>
       <c r="I5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="N5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6">
         <v>45963</v>
@@ -1724,7 +1886,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
@@ -1742,7 +1904,7 @@
         <v>45968</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>4</v>
@@ -1751,25 +1913,25 @@
         <v>4</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="6">
         <v>45970</v>
@@ -1784,10 +1946,10 @@
         <v>4</v>
       </c>
       <c r="I8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -1795,18 +1957,18 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6">
         <v>45975</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
@@ -1815,31 +1977,31 @@
         <v>4</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>45977</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
@@ -1848,10 +2010,10 @@
         <v>4</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -1859,18 +2021,18 @@
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6">
         <v>45982</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>4</v>
@@ -1879,25 +2041,25 @@
         <v>4</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6">
         <v>45984</v>
@@ -1912,25 +2074,25 @@
         <v>4</v>
       </c>
       <c r="I12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="K12" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6">
         <v>45998</v>
@@ -1940,10 +2102,10 @@
         <v>4</v>
       </c>
       <c r="I13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -1954,7 +2116,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6">
         <v>46005</v>
@@ -1969,31 +2131,31 @@
         <v>4</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="M14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="N14" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="6">
         <v>46054</v>
@@ -2005,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
@@ -2022,22 +2184,22 @@
         <v>46061</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -2045,7 +2207,7 @@
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -2056,7 +2218,7 @@
         <v>46068</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>4</v>
@@ -2065,10 +2227,10 @@
         <v>4</v>
       </c>
       <c r="I17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -2079,13 +2241,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="6">
         <v>46075</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>4</v>
@@ -2094,10 +2256,10 @@
         <v>4</v>
       </c>
       <c r="I18" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
@@ -2108,13 +2270,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="6">
         <v>46082</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>4</v>
@@ -2126,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
@@ -2137,13 +2299,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="6">
         <v>46089</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
@@ -2152,10 +2314,10 @@
         <v>4</v>
       </c>
       <c r="I20" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
@@ -2165,13 +2327,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="6">
         <v>46096</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
@@ -2183,10 +2345,10 @@
         <v>4</v>
       </c>
       <c r="I21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
@@ -2196,13 +2358,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="6">
         <v>46103</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
@@ -2214,10 +2376,10 @@
         <v>4</v>
       </c>
       <c r="I22" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
@@ -2318,7 +2480,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="14"/>
@@ -2350,16 +2512,16 @@
         <v>16</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
@@ -2367,7 +2529,7 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -2378,7 +2540,7 @@
         <v>46110</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
@@ -2390,10 +2552,10 @@
         <v>4</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
@@ -2410,7 +2572,7 @@
         <v>46117</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2422,10 +2584,10 @@
         <v>4</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
@@ -2436,13 +2598,13 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6">
         <v>46138</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
@@ -2451,7 +2613,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -2463,13 +2625,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="6">
         <v>46145</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>4</v>
@@ -2478,7 +2640,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
@@ -2490,13 +2652,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="6">
         <v>46152</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>4</v>
@@ -2508,7 +2670,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -2520,25 +2682,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="6">
         <v>46159</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>120</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -2550,13 +2712,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="6">
         <v>46166</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>4</v>
@@ -2568,7 +2730,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -2580,13 +2742,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B10" s="6">
         <v>46173</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
@@ -2598,10 +2760,10 @@
         <v>4</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -2612,13 +2774,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B11" s="6">
         <v>46180</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>4</v>
@@ -2630,10 +2792,10 @@
         <v>4</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
@@ -2644,13 +2806,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B12" s="6">
         <v>46187</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -2669,13 +2831,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B13" s="6">
         <v>46194</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>4</v>
@@ -2697,13 +2859,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B14" s="6">
         <v>46201</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
@@ -2725,13 +2887,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B15" s="6">
         <v>46236</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>4</v>
@@ -2752,13 +2914,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B16" s="6">
         <v>46243</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>4</v>
@@ -2767,10 +2929,10 @@
         <v>4</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
@@ -2781,13 +2943,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B17" s="6">
         <v>46250</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>4</v>
@@ -2799,7 +2961,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -2811,13 +2973,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B18" s="6">
         <v>46254</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>4</v>
@@ -2829,7 +2991,7 @@
         <v>4</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
@@ -2840,10 +3002,30 @@
       <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="H19" s="8"/>
+      <c r="A19" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="6">
+        <v>46264</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
@@ -2967,20 +3149,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFCB767-1FBD-9647-82C4-2908A24D9134}">
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
-    <col min="4" max="14" width="3.83203125" style="3" customWidth="1"/>
-    <col min="15" max="18" width="15.83203125" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="10.83203125" style="4"/>
+    <col min="4" max="18" width="3.83203125" style="3" customWidth="1"/>
+    <col min="19" max="22" width="15.83203125" style="3" customWidth="1"/>
+    <col min="23" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="14"/>
@@ -2999,8 +3181,12 @@
       <c r="P1" s="14"/>
       <c r="Q1" s="14"/>
       <c r="R1" s="14"/>
-    </row>
-    <row r="2" spans="1:20" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+    </row>
+    <row r="2" spans="1:24" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -3011,48 +3197,60 @@
         <v>3</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="I2" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
+        <v>156</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>194</v>
+      </c>
       <c r="S2" s="11"/>
-      <c r="T2" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -3060,7 +3258,7 @@
         <v>46229</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
@@ -3089,16 +3287,16 @@
       <c r="L3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
+      <c r="S3" s="8" t="s">
+        <v>103</v>
+      </c>
       <c r="T3" s="8"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -3106,7 +3304,7 @@
         <v>46236</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -3132,24 +3330,24 @@
       <c r="L4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
+      <c r="S4" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="T4" s="8"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6">
         <v>46243</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
@@ -3181,24 +3379,24 @@
       <c r="N5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
+      <c r="S5" s="8" t="s">
+        <v>163</v>
+      </c>
       <c r="T5" s="8"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="6">
         <v>46250</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>4</v>
@@ -3227,24 +3425,24 @@
       <c r="N6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
+      <c r="S6" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="T6" s="8"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="6">
         <v>46257</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>4</v>
@@ -3270,234 +3468,962 @@
       <c r="N7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
+      <c r="S7" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="T7" s="8"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46264</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46271</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46278</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46285</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="6">
+        <v>46292</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+    </row>
+    <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="6">
+        <v>46313</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="8"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="7"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D780A9-F75F-4337-A9DF-F8B53C76C4D6}">
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="3" customWidth="1"/>
+    <col min="4" max="7" width="3.83203125" style="3" customWidth="1"/>
+    <col min="8" max="13" width="15.83203125" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="15" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+    </row>
+    <row r="2" spans="1:15" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6">
+        <v>46271</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6">
+        <v>46278</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46285</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46289</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="6">
+        <v>46313</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
       <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
       <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
       <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
       <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
       <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-    </row>
-    <row r="13" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="8"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
       <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
       <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
       <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
       <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
